--- a/VerveStacks_KEN_grids_kan/vt_vervestacks_KEN_v1.xlsx
+++ b/VerveStacks_KEN_grids_kan/vt_vervestacks_KEN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70314AA3-9F75-4A90-8A83-112084AB466A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD6CAEDB-0547-4229-9A22-BBF54F916A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" xr2:uid="{58C35C0F-5E78-4F2D-8E85-53B5A1C0E4F1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{611109B2-678C-4D1F-9F4C-DFE0951E2F2F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1163" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="275">
   <si>
     <t>~fi_t</t>
   </si>
@@ -86,10 +86,10 @@
     <t>e_KE2-220</t>
   </si>
   <si>
-    <t>ep_bioenergy_KE2-220__ember</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_w86402221-220__ember</t>
+    <t>ep_bioenergy_KE2-220__irena</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_w86402221-220__irena</t>
   </si>
   <si>
     <t>e_w86402221-220</t>
@@ -179,9 +179,24 @@
     <t>ep_geothermal_G100001031148</t>
   </si>
   <si>
+    <t>ep_geothermal_KE7-220__irena</t>
+  </si>
+  <si>
     <t>ep_geothermal_w457973270-400</t>
   </si>
   <si>
+    <t>ep_geothermal_w457973270-400__irena</t>
+  </si>
+  <si>
+    <t>ep_geothermal_w569997185-400__irena</t>
+  </si>
+  <si>
+    <t>e_w569997185-400</t>
+  </si>
+  <si>
+    <t>ep_geothermal_w669510376-220__irena</t>
+  </si>
+  <si>
     <t>ep_hydro_KE6-220__irena</t>
   </si>
   <si>
@@ -401,12 +416,6 @@
     <t>yes</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - KE2-220_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/86402221-220_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
     <t>Menengai 1 geothermal power plant_3 -- construction</t>
   </si>
   <si>
@@ -482,6 +491,18 @@
     <t>OrPower 22 geothermal power plant_-- -- construction</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - KE7-220_Missing Geothermal Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/457973270-400_Missing Geothermal Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/569997185-400_Missing Geothermal Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/669510376-220_Missing Geothermal Capacity -- operating</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - KE6-220_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
@@ -558,9 +579,6 @@
   </si>
   <si>
     <t>en_a_geothermal_G100001005188</t>
-  </si>
-  <si>
-    <t>e_w569997185-400</t>
   </si>
   <si>
     <t>en_a_geothermal_G100001048469</t>
@@ -1216,7 +1234,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{647A33F4-C1A3-4D35-A35F-BB8BDADCD09F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{906DF3B9-7710-4C4B-9B77-E0D5D43559F0}">
   <dimension ref="B9:T18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1225,7 +1243,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.45">
@@ -1251,51 +1269,51 @@
         <v>9</v>
       </c>
       <c r="I10" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="J10" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="K10" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="L10" t="s">
         <v>10</v>
       </c>
       <c r="N10" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="O10" t="s">
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="Q10" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="R10" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="S10" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="T10" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E11">
-        <v>0.27562500000000001</v>
+        <v>0.2205</v>
       </c>
       <c r="F11">
         <v>1365</v>
@@ -1310,7 +1328,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J11" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -1319,39 +1337,39 @@
         <v>20</v>
       </c>
       <c r="N11" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O11" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="P11" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="Q11" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R11" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S11" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T11" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E12">
-        <v>0.26775000000000004</v>
+        <v>0.21420000000000006</v>
       </c>
       <c r="F12">
         <v>1365</v>
@@ -1366,7 +1384,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -1375,39 +1393,39 @@
         <v>20</v>
       </c>
       <c r="N12" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O12" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="P12" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="Q12" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R12" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S12" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T12" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E13">
-        <v>0.24806250000000002</v>
+        <v>0.19845000000000002</v>
       </c>
       <c r="F13">
         <v>1365</v>
@@ -1422,7 +1440,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J13" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -1431,39 +1449,39 @@
         <v>20</v>
       </c>
       <c r="N13" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O13" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="P13" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="Q13" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R13" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S13" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T13" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E14">
-        <v>0.26775000000000004</v>
+        <v>0.21420000000000006</v>
       </c>
       <c r="F14">
         <v>1365</v>
@@ -1478,7 +1496,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J14" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -1487,39 +1505,39 @@
         <v>20</v>
       </c>
       <c r="N14" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O14" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="P14" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="Q14" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R14" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S14" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T14" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E15">
-        <v>0.25593750000000004</v>
+        <v>0.20475000000000004</v>
       </c>
       <c r="F15">
         <v>1365</v>
@@ -1534,7 +1552,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J15" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -1543,39 +1561,39 @@
         <v>20</v>
       </c>
       <c r="N15" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O15" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="P15" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="Q15" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R15" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S15" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T15" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E16">
-        <v>0.26775000000000004</v>
+        <v>0.21420000000000006</v>
       </c>
       <c r="F16">
         <v>1365</v>
@@ -1590,7 +1608,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J16" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -1599,39 +1617,39 @@
         <v>20</v>
       </c>
       <c r="N16" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O16" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="P16" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="Q16" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R16" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S16" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T16" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E17">
-        <v>0.27562500000000001</v>
+        <v>0.2205</v>
       </c>
       <c r="F17">
         <v>1365</v>
@@ -1646,7 +1664,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J17" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -1655,39 +1673,39 @@
         <v>20</v>
       </c>
       <c r="N17" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O17" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="P17" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="Q17" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R17" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S17" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T17" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E18">
-        <v>0.27562500000000001</v>
+        <v>0.2205</v>
       </c>
       <c r="F18">
         <v>1365</v>
@@ -1702,7 +1720,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J18" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -1711,25 +1729,25 @@
         <v>20</v>
       </c>
       <c r="N18" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O18" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="P18" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="Q18" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R18" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S18" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T18" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -1738,7 +1756,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDB83AE1-E138-449A-A36F-5ABE7AE272B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48DF2DBC-6977-4729-A048-93870C15B10F}">
   <dimension ref="B9:T50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1747,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.45">
@@ -1761,10 +1779,10 @@
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="F10" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="G10" t="s">
         <v>6</v>
@@ -1785,30 +1803,30 @@
         <v>11</v>
       </c>
       <c r="N10" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="O10" t="s">
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="Q10" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="R10" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="S10" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="T10" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>
@@ -1838,36 +1856,36 @@
         <v>50</v>
       </c>
       <c r="N11" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O11" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="P11" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="Q11" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R11" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S11" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T11" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C12" t="s">
         <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>173</v>
+        <v>50</v>
       </c>
       <c r="E12">
         <v>2025</v>
@@ -1891,36 +1909,36 @@
         <v>50</v>
       </c>
       <c r="N12" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O12" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="P12" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="Q12" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R12" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S12" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T12" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E13">
         <v>2025</v>
@@ -1944,36 +1962,36 @@
         <v>50</v>
       </c>
       <c r="N13" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O13" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="P13" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="Q13" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R13" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S13" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T13" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E14">
         <v>2031</v>
@@ -1997,36 +2015,36 @@
         <v>100</v>
       </c>
       <c r="N14" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O14" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="P14" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="Q14" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R14" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S14" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T14" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D15" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E15">
         <v>2025</v>
@@ -2053,36 +2071,36 @@
         <v>0.22491019146837182</v>
       </c>
       <c r="N15" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O15" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="P15" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Q15" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R15" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S15" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T15" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E16">
         <v>2027</v>
@@ -2109,36 +2127,36 @@
         <v>0.24897163182926521</v>
       </c>
       <c r="N16" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O16" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="P16" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Q16" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R16" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S16" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T16" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E17">
         <v>2025</v>
@@ -2165,36 +2183,36 @@
         <v>0.3404851337933279</v>
       </c>
       <c r="N17" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O17" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="P17" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Q17" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R17" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S17" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T17" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E18">
         <v>2025</v>
@@ -2221,36 +2239,36 @@
         <v>0.16978404955127291</v>
       </c>
       <c r="N18" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O18" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="P18" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Q18" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R18" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S18" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T18" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E19">
         <v>2025</v>
@@ -2277,36 +2295,36 @@
         <v>9.9312871764815319E-2</v>
       </c>
       <c r="N19" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O19" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="P19" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Q19" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R19" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S19" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T19" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E20">
         <v>2025</v>
@@ -2333,36 +2351,36 @@
         <v>0.3404851337933279</v>
       </c>
       <c r="N20" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O20" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="P20" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="Q20" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R20" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S20" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T20" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E21">
         <v>2028</v>
@@ -2389,36 +2407,36 @@
         <v>0.4985435282620107</v>
       </c>
       <c r="N21" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O21" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="P21" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="Q21" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R21" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S21" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T21" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E22">
         <v>2028</v>
@@ -2442,30 +2460,30 @@
         <v>100</v>
       </c>
       <c r="N22" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O22" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="P22" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="Q22" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R22" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S22" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T22" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
@@ -2495,30 +2513,30 @@
         <v>50</v>
       </c>
       <c r="N23" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O23" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="P23" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Q23" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R23" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S23" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T23" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C24" t="s">
         <v>19</v>
@@ -2548,30 +2566,30 @@
         <v>50</v>
       </c>
       <c r="N24" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O24" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="P24" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Q24" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R24" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S24" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C25" t="s">
         <v>19</v>
@@ -2601,36 +2619,36 @@
         <v>50</v>
       </c>
       <c r="N25" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O25" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="P25" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="Q25" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R25" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S25" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T25" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C26" t="s">
         <v>19</v>
       </c>
       <c r="D26" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E26">
         <v>2028</v>
@@ -2654,30 +2672,30 @@
         <v>50</v>
       </c>
       <c r="N26" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O26" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="P26" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="Q26" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R26" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S26" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T26" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C27" t="s">
         <v>19</v>
@@ -2707,30 +2725,30 @@
         <v>50</v>
       </c>
       <c r="N27" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O27" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="P27" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="Q27" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R27" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S27" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T27" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C28" t="s">
         <v>19</v>
@@ -2760,36 +2778,36 @@
         <v>50</v>
       </c>
       <c r="N28" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O28" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="P28" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="Q28" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R28" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S28" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T28" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C29" t="s">
         <v>19</v>
       </c>
       <c r="D29" t="s">
-        <v>173</v>
+        <v>50</v>
       </c>
       <c r="E29">
         <v>2027</v>
@@ -2813,36 +2831,36 @@
         <v>50</v>
       </c>
       <c r="N29" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O29" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="P29" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="Q29" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R29" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S29" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T29" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C30" t="s">
         <v>19</v>
       </c>
       <c r="D30" t="s">
-        <v>173</v>
+        <v>50</v>
       </c>
       <c r="E30">
         <v>2030</v>
@@ -2866,36 +2884,36 @@
         <v>50</v>
       </c>
       <c r="N30" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O30" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="P30" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="Q30" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R30" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T30" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C31" t="s">
         <v>19</v>
       </c>
       <c r="D31" t="s">
-        <v>173</v>
+        <v>50</v>
       </c>
       <c r="E31">
         <v>2030</v>
@@ -2919,30 +2937,30 @@
         <v>50</v>
       </c>
       <c r="N31" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O31" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="P31" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="Q31" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R31" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S31" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T31" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C32" t="s">
         <v>19</v>
@@ -2972,36 +2990,36 @@
         <v>50</v>
       </c>
       <c r="N32" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O32" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="P32" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="Q32" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R32" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S32" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T32" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C33" t="s">
         <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E33">
         <v>2027</v>
@@ -3025,30 +3043,30 @@
         <v>50</v>
       </c>
       <c r="N33" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O33" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="P33" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="Q33" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R33" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S33" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T33" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="C34" t="s">
         <v>19</v>
@@ -3078,36 +3096,36 @@
         <v>50</v>
       </c>
       <c r="N34" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O34" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="P34" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="Q34" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R34" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S34" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T34" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C35" t="s">
         <v>19</v>
       </c>
       <c r="D35" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E35">
         <v>2025</v>
@@ -3131,36 +3149,36 @@
         <v>50</v>
       </c>
       <c r="N35" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O35" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="P35" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="Q35" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R35" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S35" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T35" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C36" t="s">
         <v>19</v>
       </c>
       <c r="D36" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E36">
         <v>2025</v>
@@ -3184,36 +3202,36 @@
         <v>50</v>
       </c>
       <c r="N36" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O36" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="P36" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="Q36" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R36" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S36" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T36" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C37" t="s">
         <v>19</v>
       </c>
       <c r="D37" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E37">
         <v>2025</v>
@@ -3237,36 +3255,36 @@
         <v>50</v>
       </c>
       <c r="N37" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O37" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="P37" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="Q37" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R37" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S37" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T37" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C38" t="s">
         <v>19</v>
       </c>
       <c r="D38" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E38">
         <v>2025</v>
@@ -3290,36 +3308,36 @@
         <v>50</v>
       </c>
       <c r="N38" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O38" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="P38" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="Q38" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R38" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S38" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T38" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C39" t="s">
         <v>19</v>
       </c>
       <c r="D39" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E39">
         <v>2025</v>
@@ -3343,36 +3361,36 @@
         <v>50</v>
       </c>
       <c r="N39" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O39" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="P39" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="Q39" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R39" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S39" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T39" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C40" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D40" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E40">
         <v>2031</v>
@@ -3396,36 +3414,36 @@
         <v>100</v>
       </c>
       <c r="N40" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O40" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="P40" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="Q40" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R40" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S40" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T40" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C41" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D41" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E41">
         <v>2025</v>
@@ -3449,36 +3467,36 @@
         <v>100</v>
       </c>
       <c r="N41" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O41" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="P41" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="Q41" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R41" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S41" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T41" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C42" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D42" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="E42">
         <v>2027</v>
@@ -3502,36 +3520,36 @@
         <v>50</v>
       </c>
       <c r="N42" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O42" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="P42" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="Q42" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R42" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S42" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T42" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="43" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C43" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D43" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="E43">
         <v>2035</v>
@@ -3555,36 +3573,36 @@
         <v>50</v>
       </c>
       <c r="N43" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O43" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="P43" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="Q43" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R43" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S43" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T43" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C44" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D44" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E44">
         <v>2026</v>
@@ -3611,36 +3629,36 @@
         <v>0.2301224015067071</v>
       </c>
       <c r="N44" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O44" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="P44" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Q44" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R44" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S44" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T44" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C45" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D45" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E45">
         <v>2025</v>
@@ -3667,36 +3685,36 @@
         <v>0.23354545132238788</v>
       </c>
       <c r="N45" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O45" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="P45" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Q45" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R45" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S45" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T45" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C46" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D46" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E46">
         <v>2028</v>
@@ -3723,36 +3741,36 @@
         <v>0.46618534352849123</v>
       </c>
       <c r="N46" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O46" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="P46" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Q46" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R46" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S46" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T46" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C47" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D47" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E47">
         <v>2030</v>
@@ -3779,36 +3797,36 @@
         <v>0.46618534352849128</v>
       </c>
       <c r="N47" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O47" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="P47" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Q47" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R47" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S47" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T47" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C48" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D48" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="E48">
         <v>2025</v>
@@ -3835,36 +3853,36 @@
         <v>0.33056297534614321</v>
       </c>
       <c r="N48" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O48" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="P48" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Q48" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R48" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S48" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T48" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C49" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D49" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E49">
         <v>2025</v>
@@ -3891,36 +3909,36 @@
         <v>9.6003187650629498E-2</v>
       </c>
       <c r="N49" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O49" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="P49" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Q49" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R49" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S49" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T49" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C50" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D50" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E50">
         <v>2026</v>
@@ -3953,8 +3971,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5CF5F44-76E2-4252-998E-5F6AFDE46924}">
-  <dimension ref="B9:T75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8474A348-D0EB-441C-AF0D-FD861A7B5D08}">
+  <dimension ref="B9:T79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="2:20" x14ac:dyDescent="0.45">
@@ -3962,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.45">
@@ -4000,25 +4018,25 @@
         <v>11</v>
       </c>
       <c r="N10" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="O10" t="s">
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="Q10" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="R10" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="S10" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="T10" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.45">
@@ -4038,7 +4056,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="G11">
-        <v>0.216</v>
+        <v>0.17280000000000001</v>
       </c>
       <c r="H11">
         <v>4016.25</v>
@@ -4053,25 +4071,25 @@
         <v>84</v>
       </c>
       <c r="N11" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O11" t="s">
         <v>12</v>
       </c>
       <c r="P11" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q11" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R11" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S11" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T11" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.45">
@@ -4088,25 +4106,25 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>0.43726582278481013</v>
+        <v>2.7847291139240511E-2</v>
       </c>
       <c r="G12">
-        <v>0.315</v>
+        <v>0.23040000000000005</v>
       </c>
       <c r="H12">
-        <v>2974.9999999999995</v>
+        <v>4016.25</v>
       </c>
       <c r="I12">
-        <v>116.99999999999999</v>
+        <v>152.1</v>
       </c>
       <c r="J12">
-        <v>7.1999999999999993</v>
+        <v>8.64</v>
       </c>
       <c r="K12">
         <v>50</v>
       </c>
       <c r="N12" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O12" t="s">
         <v>15</v>
@@ -4115,16 +4133,16 @@
         <v>120</v>
       </c>
       <c r="Q12" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R12" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S12" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T12" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.45">
@@ -4141,43 +4159,43 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>0.57873417721518994</v>
+        <v>3.6856708860759493E-2</v>
       </c>
       <c r="G13">
-        <v>0.315</v>
+        <v>0.23040000000000008</v>
       </c>
       <c r="H13">
-        <v>2975</v>
+        <v>4016.25</v>
       </c>
       <c r="I13">
-        <v>117</v>
+        <v>152.1</v>
       </c>
       <c r="J13">
-        <v>7.2</v>
+        <v>8.64</v>
       </c>
       <c r="K13">
         <v>50</v>
       </c>
       <c r="N13" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O13" t="s">
         <v>16</v>
       </c>
       <c r="P13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q13" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R13" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S13" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T13" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.45">
@@ -4212,25 +4230,25 @@
         <v>50</v>
       </c>
       <c r="N14" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O14" t="s">
         <v>18</v>
       </c>
       <c r="P14" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="Q14" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R14" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S14" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T14" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.45">
@@ -4265,25 +4283,25 @@
         <v>50</v>
       </c>
       <c r="N15" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O15" t="s">
         <v>21</v>
       </c>
       <c r="P15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="Q15" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R15" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S15" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T15" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.45">
@@ -4318,25 +4336,25 @@
         <v>50</v>
       </c>
       <c r="N16" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O16" t="s">
         <v>22</v>
       </c>
       <c r="P16" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="Q16" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R16" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S16" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T16" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.45">
@@ -4371,25 +4389,25 @@
         <v>50</v>
       </c>
       <c r="N17" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O17" t="s">
         <v>23</v>
       </c>
       <c r="P17" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>121</v>
+      </c>
+      <c r="R17" t="s">
+        <v>122</v>
+      </c>
+      <c r="S17" t="s">
+        <v>123</v>
+      </c>
+      <c r="T17" t="s">
         <v>126</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>116</v>
-      </c>
-      <c r="R17" t="s">
-        <v>117</v>
-      </c>
-      <c r="S17" t="s">
-        <v>118</v>
-      </c>
-      <c r="T17" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.45">
@@ -4424,25 +4442,25 @@
         <v>50</v>
       </c>
       <c r="N18" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O18" t="s">
         <v>25</v>
       </c>
       <c r="P18" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Q18" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R18" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S18" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T18" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.45">
@@ -4477,25 +4495,25 @@
         <v>50</v>
       </c>
       <c r="N19" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O19" t="s">
         <v>26</v>
       </c>
       <c r="P19" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Q19" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R19" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S19" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T19" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.45">
@@ -4530,25 +4548,25 @@
         <v>52</v>
       </c>
       <c r="N20" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O20" t="s">
         <v>27</v>
       </c>
       <c r="P20" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Q20" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R20" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S20" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T20" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.45">
@@ -4583,25 +4601,25 @@
         <v>52</v>
       </c>
       <c r="N21" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O21" t="s">
         <v>28</v>
       </c>
       <c r="P21" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="Q21" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R21" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S21" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T21" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.45">
@@ -4636,25 +4654,25 @@
         <v>50</v>
       </c>
       <c r="N22" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O22" t="s">
         <v>29</v>
       </c>
       <c r="P22" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="Q22" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R22" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S22" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T22" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.45">
@@ -4689,25 +4707,25 @@
         <v>55</v>
       </c>
       <c r="N23" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O23" t="s">
         <v>30</v>
       </c>
       <c r="P23" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="Q23" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R23" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S23" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T23" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.45">
@@ -4742,25 +4760,25 @@
         <v>50</v>
       </c>
       <c r="N24" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O24" t="s">
         <v>31</v>
       </c>
       <c r="P24" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q24" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R24" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S24" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.45">
@@ -4795,25 +4813,25 @@
         <v>50</v>
       </c>
       <c r="N25" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O25" t="s">
         <v>32</v>
       </c>
       <c r="P25" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="Q25" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R25" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S25" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T25" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.45">
@@ -4848,25 +4866,25 @@
         <v>50</v>
       </c>
       <c r="N26" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O26" t="s">
         <v>34</v>
       </c>
       <c r="P26" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="Q26" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R26" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S26" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T26" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.45">
@@ -4901,25 +4919,25 @@
         <v>50</v>
       </c>
       <c r="N27" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O27" t="s">
         <v>35</v>
       </c>
       <c r="P27" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="Q27" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R27" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S27" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T27" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.45">
@@ -4954,25 +4972,25 @@
         <v>50</v>
       </c>
       <c r="N28" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O28" t="s">
         <v>36</v>
       </c>
       <c r="P28" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="Q28" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R28" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S28" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T28" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.45">
@@ -5007,25 +5025,25 @@
         <v>42</v>
       </c>
       <c r="N29" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O29" t="s">
         <v>37</v>
       </c>
       <c r="P29" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="Q29" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R29" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S29" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T29" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.45">
@@ -5060,25 +5078,25 @@
         <v>41</v>
       </c>
       <c r="N30" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O30" t="s">
         <v>38</v>
       </c>
       <c r="P30" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="Q30" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R30" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T30" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.45">
@@ -5113,25 +5131,25 @@
         <v>38</v>
       </c>
       <c r="N31" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O31" t="s">
         <v>39</v>
       </c>
       <c r="P31" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="Q31" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R31" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S31" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T31" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.45">
@@ -5166,25 +5184,25 @@
         <v>50</v>
       </c>
       <c r="N32" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O32" t="s">
         <v>40</v>
       </c>
       <c r="P32" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="Q32" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R32" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S32" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T32" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="2:20" x14ac:dyDescent="0.45">
@@ -5219,25 +5237,25 @@
         <v>50</v>
       </c>
       <c r="N33" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O33" t="s">
         <v>41</v>
       </c>
       <c r="P33" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="Q33" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R33" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S33" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T33" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.45">
@@ -5272,25 +5290,25 @@
         <v>50</v>
       </c>
       <c r="N34" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O34" t="s">
         <v>42</v>
       </c>
       <c r="P34" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Q34" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R34" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S34" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T34" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.45">
@@ -5325,25 +5343,25 @@
         <v>50</v>
       </c>
       <c r="N35" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O35" t="s">
         <v>43</v>
       </c>
       <c r="P35" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q35" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R35" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S35" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T35" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.45">
@@ -5378,25 +5396,25 @@
         <v>50</v>
       </c>
       <c r="N36" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O36" t="s">
         <v>44</v>
       </c>
       <c r="P36" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Q36" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R36" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S36" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T36" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.45">
@@ -5431,25 +5449,25 @@
         <v>50</v>
       </c>
       <c r="N37" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O37" t="s">
         <v>45</v>
       </c>
       <c r="P37" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q37" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R37" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S37" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T37" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.45">
@@ -5460,13 +5478,13 @@
         <v>19</v>
       </c>
       <c r="D38" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E38">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="F38">
-        <v>2.5000000000000001E-3</v>
+        <v>2.1763879549233318E-2</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -5484,25 +5502,25 @@
         <v>50</v>
       </c>
       <c r="N38" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O38" t="s">
         <v>46</v>
       </c>
       <c r="P38" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="Q38" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R38" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S38" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T38" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.45">
@@ -5510,734 +5528,734 @@
         <v>47</v>
       </c>
       <c r="C39" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="D39" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E39">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="F39">
-        <v>2.5341064841498579E-2</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G39">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>4819.5</v>
+      </c>
+      <c r="I39">
+        <v>152.1</v>
+      </c>
+      <c r="J39">
+        <v>2.7</v>
       </c>
       <c r="K39">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="N39" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O39" t="s">
         <v>47</v>
       </c>
       <c r="P39" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="Q39" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R39" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S39" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T39" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40">
+        <v>2022</v>
+      </c>
+      <c r="F40">
+        <v>6.941220580084978E-2</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <v>4105.5</v>
+      </c>
+      <c r="I40">
+        <v>128.70000000000002</v>
+      </c>
+      <c r="J40">
+        <v>2.4750000000000001</v>
+      </c>
+      <c r="K40">
         <v>50</v>
       </c>
-      <c r="C40" t="s">
+      <c r="N40" t="s">
+        <v>119</v>
+      </c>
+      <c r="O40" t="s">
         <v>48</v>
       </c>
-      <c r="D40" t="s">
-        <v>51</v>
-      </c>
-      <c r="E40">
-        <v>1974</v>
-      </c>
-      <c r="F40">
-        <v>9.4E-2</v>
-      </c>
-      <c r="G40">
-        <v>1</v>
-      </c>
-      <c r="H40">
-        <v>2443.75</v>
-      </c>
-      <c r="I40">
-        <v>49.500000000000007</v>
-      </c>
-      <c r="J40">
-        <v>1.9800000000000004</v>
-      </c>
-      <c r="K40">
-        <v>100</v>
-      </c>
-      <c r="N40" t="s">
-        <v>114</v>
-      </c>
-      <c r="O40" t="s">
-        <v>50</v>
-      </c>
       <c r="P40" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q40" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R40" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S40" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T40" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C41" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="D41" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E41">
-        <v>1988</v>
+        <v>2022</v>
       </c>
       <c r="F41">
-        <v>0.16800000000000001</v>
+        <v>1.3659338629225932E-2</v>
       </c>
       <c r="G41">
         <v>1</v>
       </c>
       <c r="H41">
-        <v>2443.75</v>
+        <v>4819.5</v>
       </c>
       <c r="I41">
-        <v>49.500000000000014</v>
+        <v>152.1</v>
       </c>
       <c r="J41">
-        <v>1.9800000000000002</v>
+        <v>2.7</v>
       </c>
       <c r="K41">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N41" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O41" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="P41" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q41" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R41" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S41" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T41" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="D42" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="E42">
-        <v>1991</v>
+        <v>2022</v>
       </c>
       <c r="F42">
-        <v>0.10299999999999999</v>
+        <v>1.839457602069092E-2</v>
       </c>
       <c r="G42">
         <v>1</v>
       </c>
       <c r="H42">
-        <v>2443.75</v>
+        <v>4819.5</v>
       </c>
       <c r="I42">
-        <v>49.500000000000007</v>
+        <v>152.1</v>
       </c>
       <c r="J42">
-        <v>1.9800000000000002</v>
+        <v>2.7</v>
       </c>
       <c r="K42">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N42" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O42" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="P42" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q42" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R42" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S42" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T42" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D43" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E43">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="F43">
-        <v>7.1999999999999995E-2</v>
+        <v>2.5341064841498579E-2</v>
       </c>
       <c r="G43">
-        <v>1</v>
-      </c>
-      <c r="H43">
-        <v>2443.75</v>
-      </c>
-      <c r="I43">
-        <v>49.500000000000007</v>
-      </c>
-      <c r="J43">
-        <v>1.98</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="K43">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="N43" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O43" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="P43" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q43" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R43" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S43" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T43" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C44" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D44" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E44">
-        <v>1978</v>
+        <v>1974</v>
       </c>
       <c r="F44">
-        <v>0.22500000000000001</v>
+        <v>9.4E-2</v>
       </c>
       <c r="G44">
         <v>1</v>
       </c>
       <c r="H44">
-        <v>2150.5</v>
+        <v>2443.75</v>
       </c>
       <c r="I44">
-        <v>54.45000000000001</v>
+        <v>49.500000000000007</v>
       </c>
       <c r="J44">
-        <v>2.4750000000000001</v>
+        <v>1.9800000000000004</v>
       </c>
       <c r="K44">
         <v>100</v>
       </c>
       <c r="N44" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O44" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="P44" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q44" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R44" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S44" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T44" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45" t="s">
         <v>58</v>
       </c>
-      <c r="C45" t="s">
-        <v>48</v>
-      </c>
-      <c r="D45" t="s">
-        <v>59</v>
-      </c>
       <c r="E45">
-        <v>2008</v>
+        <v>1988</v>
       </c>
       <c r="F45">
-        <v>0.06</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="G45">
         <v>1</v>
       </c>
       <c r="H45">
-        <v>2150.5</v>
+        <v>2443.75</v>
       </c>
       <c r="I45">
-        <v>54.45000000000001</v>
+        <v>49.500000000000014</v>
       </c>
       <c r="J45">
-        <v>2.4750000000000001</v>
+        <v>1.9800000000000002</v>
       </c>
       <c r="K45">
         <v>100</v>
       </c>
       <c r="N45" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O45" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P45" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q45" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R45" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S45" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T45" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46" t="s">
+        <v>53</v>
+      </c>
+      <c r="D46" t="s">
         <v>60</v>
       </c>
-      <c r="C46" t="s">
-        <v>48</v>
-      </c>
-      <c r="D46" t="s">
-        <v>61</v>
-      </c>
       <c r="E46">
-        <v>2028</v>
+        <v>1991</v>
       </c>
       <c r="F46">
-        <v>0.06</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="G46">
         <v>1</v>
       </c>
       <c r="H46">
-        <v>2150.5</v>
+        <v>2443.75</v>
       </c>
       <c r="I46">
-        <v>54.45000000000001</v>
+        <v>49.500000000000007</v>
       </c>
       <c r="J46">
-        <v>2.4750000000000001</v>
+        <v>1.9800000000000002</v>
       </c>
       <c r="K46">
         <v>100</v>
       </c>
       <c r="N46" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P46" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q46" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R46" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S46" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T46" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D47" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E47">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="F47">
-        <v>1.1786541786743524E-2</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="G47">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="H47">
+        <v>2443.75</v>
+      </c>
+      <c r="I47">
+        <v>49.500000000000007</v>
+      </c>
+      <c r="J47">
+        <v>1.98</v>
       </c>
       <c r="K47">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="N47" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O47" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P47" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q47" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R47" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S47" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T47" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C48" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D48" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E48">
-        <v>2022</v>
+        <v>1978</v>
       </c>
       <c r="F48">
-        <v>9.9203393371757986E-2</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="G48">
-        <v>0.33122999999999997</v>
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>2150.5</v>
+      </c>
+      <c r="I48">
+        <v>54.45000000000001</v>
+      </c>
+      <c r="J48">
+        <v>2.4750000000000001</v>
       </c>
       <c r="K48">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="N48" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P48" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q48" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R48" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S48" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T48" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
+        <v>63</v>
+      </c>
+      <c r="C49" t="s">
+        <v>53</v>
+      </c>
+      <c r="D49" t="s">
         <v>64</v>
       </c>
-      <c r="C49" t="s">
-        <v>65</v>
-      </c>
-      <c r="D49" t="s">
-        <v>66</v>
-      </c>
       <c r="E49">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="F49">
-        <v>8.6999999999999994E-2</v>
+        <v>0.06</v>
       </c>
       <c r="G49">
-        <v>0.315</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>977.5</v>
+        <v>2150.5</v>
       </c>
       <c r="I49">
-        <v>39.6</v>
+        <v>54.45000000000001</v>
       </c>
       <c r="J49">
-        <v>6.4350000000000005</v>
+        <v>2.4750000000000001</v>
       </c>
       <c r="K49">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="N49" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P49" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q49" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R49" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S49" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T49" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D50" t="s">
+        <v>66</v>
+      </c>
+      <c r="E50">
+        <v>2028</v>
+      </c>
+      <c r="F50">
+        <v>0.06</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50">
+        <v>2150.5</v>
+      </c>
+      <c r="I50">
+        <v>54.45000000000001</v>
+      </c>
+      <c r="J50">
+        <v>2.4750000000000001</v>
+      </c>
+      <c r="K50">
+        <v>100</v>
+      </c>
+      <c r="N50" t="s">
+        <v>119</v>
+      </c>
+      <c r="O50" t="s">
         <v>65</v>
       </c>
-      <c r="D50" t="s">
-        <v>68</v>
-      </c>
-      <c r="E50">
-        <v>2009</v>
-      </c>
-      <c r="F50">
-        <v>8.5000000000000006E-2</v>
-      </c>
-      <c r="G50">
-        <v>0.30600000000000005</v>
-      </c>
-      <c r="H50">
-        <v>977.5</v>
-      </c>
-      <c r="I50">
-        <v>39.6</v>
-      </c>
-      <c r="J50">
-        <v>6.4350000000000005</v>
-      </c>
-      <c r="K50">
-        <v>21</v>
-      </c>
-      <c r="N50" t="s">
-        <v>114</v>
-      </c>
-      <c r="O50" t="s">
-        <v>67</v>
-      </c>
       <c r="P50" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q50" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R50" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S50" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T50" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C51" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D51" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E51">
-        <v>1987</v>
+        <v>2022</v>
       </c>
       <c r="F51">
-        <v>0.06</v>
+        <v>1.1786541786743524E-2</v>
       </c>
       <c r="G51">
-        <v>0.28350000000000003</v>
-      </c>
-      <c r="H51">
-        <v>977.5</v>
-      </c>
-      <c r="I51">
-        <v>39.6</v>
-      </c>
-      <c r="J51">
-        <v>6.4350000000000005</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="K51">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="N51" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O51" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P51" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q51" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R51" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S51" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T51" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C52" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D52" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="E52">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="F52">
-        <v>0.1169</v>
+        <v>9.9203393371757986E-2</v>
       </c>
       <c r="G52">
-        <v>0.30600000000000005</v>
-      </c>
-      <c r="H52">
-        <v>977.5</v>
-      </c>
-      <c r="I52">
-        <v>39.6</v>
-      </c>
-      <c r="J52">
-        <v>6.4350000000000005</v>
+        <v>0.33122999999999997</v>
       </c>
       <c r="K52">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="N52" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O52" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P52" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q52" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R52" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S52" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T52" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C53" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D53" t="s">
         <v>71</v>
       </c>
       <c r="E53">
-        <v>1999</v>
+        <v>2013</v>
       </c>
       <c r="F53">
-        <v>7.3999999999999996E-2</v>
+        <v>8.6999999999999994E-2</v>
       </c>
       <c r="G53">
-        <v>0.29250000000000004</v>
+        <v>0.252</v>
       </c>
       <c r="H53">
         <v>977.5</v>
@@ -6249,48 +6267,48 @@
         <v>6.4350000000000005</v>
       </c>
       <c r="K53">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N53" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O53" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P53" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q53" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R53" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S53" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T53" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
+        <v>72</v>
+      </c>
+      <c r="C54" t="s">
+        <v>70</v>
+      </c>
+      <c r="D54" t="s">
         <v>73</v>
       </c>
-      <c r="C54" t="s">
-        <v>65</v>
-      </c>
-      <c r="D54" t="s">
-        <v>74</v>
-      </c>
       <c r="E54">
-        <v>2004</v>
+        <v>2009</v>
       </c>
       <c r="F54">
-        <v>5.2999999999999999E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="G54">
-        <v>0.30600000000000005</v>
+        <v>0.24480000000000005</v>
       </c>
       <c r="H54">
         <v>977.5</v>
@@ -6302,48 +6320,48 @@
         <v>6.4350000000000005</v>
       </c>
       <c r="K54">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="N54" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O54" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P54" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q54" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R54" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S54" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T54" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C55" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D55" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E55">
-        <v>2015</v>
+        <v>1987</v>
       </c>
       <c r="F55">
-        <v>8.3199999999999996E-2</v>
+        <v>0.06</v>
       </c>
       <c r="G55">
-        <v>0.315</v>
+        <v>0.22680000000000003</v>
       </c>
       <c r="H55">
         <v>977.5</v>
@@ -6355,48 +6373,48 @@
         <v>6.4350000000000005</v>
       </c>
       <c r="K55">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="N55" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O55" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P55" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q55" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R55" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S55" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T55" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C56" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D56" t="s">
         <v>76</v>
       </c>
       <c r="E56">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="F56">
-        <v>0.08</v>
+        <v>0.1169</v>
       </c>
       <c r="G56">
-        <v>0.315</v>
+        <v>0.24480000000000005</v>
       </c>
       <c r="H56">
         <v>977.5</v>
@@ -6408,410 +6426,398 @@
         <v>6.4350000000000005</v>
       </c>
       <c r="K56">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N56" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O56" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P56" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q56" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R56" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S56" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C57" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D57" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E57">
-        <v>2022</v>
+        <v>1999</v>
       </c>
       <c r="F57">
-        <v>2.2195369641804075E-2</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="G57">
-        <v>0.33123000000000002</v>
+        <v>0.23400000000000004</v>
+      </c>
+      <c r="H57">
+        <v>977.5</v>
+      </c>
+      <c r="I57">
+        <v>39.6</v>
+      </c>
+      <c r="J57">
+        <v>6.4350000000000005</v>
       </c>
       <c r="K57">
-        <v>33</v>
-      </c>
-      <c r="L57">
-        <v>0.2386419197277922</v>
+        <v>24</v>
       </c>
       <c r="N57" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O57" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P57" t="s">
-        <v>115</v>
+        <v>168</v>
       </c>
       <c r="Q57" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R57" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S57" t="s">
-        <v>165</v>
+        <v>123</v>
       </c>
       <c r="T57" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C58" t="s">
+        <v>70</v>
+      </c>
+      <c r="D58" t="s">
         <v>79</v>
       </c>
-      <c r="D58" t="s">
-        <v>82</v>
-      </c>
       <c r="E58">
-        <v>2022</v>
+        <v>2004</v>
       </c>
       <c r="F58">
-        <v>1.9490684055002715E-2</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="G58">
-        <v>0.33123000000000002</v>
+        <v>0.24480000000000005</v>
+      </c>
+      <c r="H58">
+        <v>977.5</v>
+      </c>
+      <c r="I58">
+        <v>39.6</v>
+      </c>
+      <c r="J58">
+        <v>6.4350000000000005</v>
       </c>
       <c r="K58">
-        <v>33</v>
-      </c>
-      <c r="L58">
-        <v>0.2386419197277922</v>
+        <v>30</v>
       </c>
       <c r="N58" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O58" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="P58" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="Q58" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R58" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S58" t="s">
-        <v>165</v>
+        <v>123</v>
       </c>
       <c r="T58" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C59" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D59" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E59">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="F59">
-        <v>1.9760946303193187E-2</v>
+        <v>8.3199999999999996E-2</v>
       </c>
       <c r="G59">
-        <v>0.33123000000000002</v>
+        <v>0.252</v>
+      </c>
+      <c r="H59">
+        <v>977.5</v>
+      </c>
+      <c r="I59">
+        <v>39.6</v>
+      </c>
+      <c r="J59">
+        <v>6.4350000000000005</v>
       </c>
       <c r="K59">
-        <v>33</v>
-      </c>
-      <c r="L59">
-        <v>0.2386419197277922</v>
+        <v>20</v>
       </c>
       <c r="N59" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O59" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P59" t="s">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="Q59" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R59" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S59" t="s">
-        <v>165</v>
+        <v>123</v>
       </c>
       <c r="T59" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="60" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C60" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D60" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E60">
-        <v>2028</v>
+        <v>2014</v>
       </c>
       <c r="F60">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>0.252</v>
       </c>
       <c r="H60">
-        <v>1032.75</v>
+        <v>977.5</v>
       </c>
       <c r="I60">
-        <v>17.55</v>
+        <v>39.6</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>6.4350000000000005</v>
       </c>
       <c r="K60">
-        <v>30</v>
-      </c>
-      <c r="L60">
-        <v>0.2301224015067071</v>
+        <v>20</v>
       </c>
       <c r="N60" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O60" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P60" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="Q60" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R60" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S60" t="s">
-        <v>165</v>
+        <v>123</v>
       </c>
       <c r="T60" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="61" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C61" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D61" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E61">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F61">
-        <v>0.04</v>
+        <v>2.2195369641804075E-2</v>
       </c>
       <c r="G61">
-        <v>1</v>
-      </c>
-      <c r="H61">
-        <v>1032.75</v>
-      </c>
-      <c r="I61">
-        <v>17.55</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="K61">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L61">
-        <v>0.25369869095953879</v>
+        <v>0.2386419197277922</v>
       </c>
       <c r="N61" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O61" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="P61" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q61" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R61" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S61" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T61" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="62" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
+        <v>86</v>
+      </c>
+      <c r="C62" t="s">
+        <v>84</v>
+      </c>
+      <c r="D62" t="s">
         <v>87</v>
       </c>
-      <c r="C62" t="s">
-        <v>79</v>
-      </c>
-      <c r="D62" t="s">
-        <v>88</v>
-      </c>
       <c r="E62">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F62">
-        <v>0.04</v>
+        <v>1.9490684055002715E-2</v>
       </c>
       <c r="G62">
-        <v>1</v>
-      </c>
-      <c r="H62">
-        <v>1032.75</v>
-      </c>
-      <c r="I62">
-        <v>17.55</v>
-      </c>
-      <c r="J62">
-        <v>0</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="K62">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L62">
-        <v>0.25369869095953879</v>
+        <v>0.2386419197277922</v>
       </c>
       <c r="N62" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O62" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P62" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="Q62" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R62" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S62" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T62" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="63" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C63" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D63" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E63">
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>0.04</v>
+        <v>1.9760946303193187E-2</v>
       </c>
       <c r="G63">
-        <v>1</v>
-      </c>
-      <c r="H63">
-        <v>1032.75</v>
-      </c>
-      <c r="I63">
-        <v>17.55</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="K63">
         <v>33</v>
       </c>
       <c r="L63">
-        <v>0.25369869095953879</v>
+        <v>0.2386419197277922</v>
       </c>
       <c r="N63" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O63" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P63" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q63" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R63" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S63" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T63" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="64" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C64" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D64" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E64">
-        <v>2021</v>
+        <v>2028</v>
       </c>
       <c r="F64">
-        <v>1.0999999999999999E-2</v>
+        <v>0.04</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -6826,45 +6832,45 @@
         <v>0</v>
       </c>
       <c r="K64">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L64">
-        <v>0.23354545132238791</v>
+        <v>0.2301224015067071</v>
       </c>
       <c r="N64" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O64" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P64" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="Q64" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R64" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S64" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T64" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C65" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D65" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E65">
-        <v>2028</v>
+        <v>2015</v>
       </c>
       <c r="F65">
         <v>0.04</v>
@@ -6882,45 +6888,45 @@
         <v>0</v>
       </c>
       <c r="K65">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L65">
-        <v>0.23354545132238788</v>
+        <v>0.25369869095953879</v>
       </c>
       <c r="N65" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O65" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P65" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q65" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R65" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S65" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T65" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="66" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C66" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D66" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E66">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F66">
         <v>0.04</v>
@@ -6938,104 +6944,104 @@
         <v>0</v>
       </c>
       <c r="K66">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L66">
-        <v>0.22878422375200849</v>
+        <v>0.25369869095953879</v>
       </c>
       <c r="N66" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O66" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P66" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="Q66" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R66" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S66" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T66" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="67" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
+        <v>92</v>
+      </c>
+      <c r="C67" t="s">
+        <v>84</v>
+      </c>
+      <c r="D67" t="s">
         <v>93</v>
       </c>
-      <c r="C67" t="s">
-        <v>79</v>
-      </c>
-      <c r="D67" t="s">
-        <v>94</v>
-      </c>
       <c r="E67">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="F67">
-        <v>5.3999999999999999E-2</v>
+        <v>0.04</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
       <c r="H67">
-        <v>879.75</v>
+        <v>1032.75</v>
       </c>
       <c r="I67">
-        <v>14.85</v>
+        <v>17.55</v>
       </c>
       <c r="J67">
         <v>0</v>
       </c>
       <c r="K67">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="L67">
-        <v>0.2357479849120028</v>
+        <v>0.25369869095953879</v>
       </c>
       <c r="N67" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O67" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P67" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q67" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R67" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S67" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T67" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="68" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
+        <v>94</v>
+      </c>
+      <c r="C68" t="s">
+        <v>84</v>
+      </c>
+      <c r="D68" t="s">
         <v>95</v>
       </c>
-      <c r="C68" t="s">
-        <v>79</v>
-      </c>
-      <c r="D68" t="s">
-        <v>96</v>
-      </c>
       <c r="E68">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F68">
-        <v>3.2000000000000001E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -7050,234 +7056,255 @@
         <v>0</v>
       </c>
       <c r="K68">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L68">
-        <v>0.24195369464045599</v>
+        <v>0.23354545132238791</v>
       </c>
       <c r="N68" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O68" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P68" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q68" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R68" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S68" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T68" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C69" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D69" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E69">
-        <v>2021</v>
+        <v>2028</v>
       </c>
       <c r="F69">
-        <v>3.5999999999999997E-2</v>
+        <v>0.04</v>
       </c>
       <c r="G69">
         <v>1</v>
       </c>
       <c r="H69">
-        <v>1836</v>
+        <v>1032.75</v>
       </c>
       <c r="I69">
-        <v>46.800000000000004</v>
+        <v>17.55</v>
       </c>
       <c r="J69">
         <v>0</v>
       </c>
       <c r="K69">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L69">
-        <v>0.33309194745150211</v>
+        <v>0.23354545132238788</v>
       </c>
       <c r="N69" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O69" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="P69" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q69" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R69" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S69" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T69" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="70" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C70" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D70" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E70">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="F70">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G70">
         <v>1</v>
       </c>
       <c r="H70">
-        <v>1836</v>
+        <v>1032.75</v>
       </c>
       <c r="I70">
-        <v>46.8</v>
+        <v>17.55</v>
       </c>
       <c r="J70">
         <v>0</v>
       </c>
       <c r="K70">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L70">
-        <v>0.4985435282620107</v>
+        <v>0.22878422375200849</v>
       </c>
       <c r="N70" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O70" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="P70" t="s">
-        <v>167</v>
+        <v>120</v>
       </c>
       <c r="Q70" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R70" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S70" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T70" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="71" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C71" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D71" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E71">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="F71">
-        <v>1.4E-2</v>
+        <v>5.3999999999999999E-2</v>
       </c>
       <c r="G71">
         <v>1</v>
       </c>
       <c r="H71">
-        <v>1836</v>
+        <v>879.75</v>
       </c>
       <c r="I71">
-        <v>46.800000000000004</v>
+        <v>14.85</v>
       </c>
       <c r="J71">
         <v>0</v>
       </c>
       <c r="K71">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="L71">
-        <v>9.9312871764815305E-2</v>
+        <v>0.2357479849120028</v>
       </c>
       <c r="N71" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O71" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="P71" t="s">
-        <v>168</v>
+        <v>120</v>
       </c>
       <c r="Q71" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R71" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S71" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="T71" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="72" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C72" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D72" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E72">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F72">
-        <v>1.15E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="G72">
         <v>1</v>
       </c>
       <c r="H72">
-        <v>1836</v>
+        <v>1032.75</v>
       </c>
       <c r="I72">
-        <v>46.800000000000004</v>
+        <v>17.55</v>
       </c>
       <c r="J72">
         <v>0</v>
       </c>
       <c r="K72">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L72">
-        <v>9.9312871764815305E-2</v>
+        <v>0.24195369464045599</v>
+      </c>
+      <c r="N72" t="s">
+        <v>119</v>
+      </c>
+      <c r="O72" t="s">
+        <v>105</v>
+      </c>
+      <c r="P72" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>121</v>
+      </c>
+      <c r="R72" t="s">
+        <v>122</v>
+      </c>
+      <c r="S72" t="s">
+        <v>172</v>
+      </c>
+      <c r="T72" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="73" spans="2:20" x14ac:dyDescent="0.45">
@@ -7285,25 +7312,25 @@
         <v>102</v>
       </c>
       <c r="C73" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D73" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E73">
         <v>2021</v>
       </c>
       <c r="F73">
-        <v>0.161</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="G73">
         <v>1</v>
       </c>
       <c r="H73">
-        <v>1667.0559006211181</v>
+        <v>1836</v>
       </c>
       <c r="I73">
-        <v>42.327950310559004</v>
+        <v>46.800000000000004</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -7312,33 +7339,54 @@
         <v>34</v>
       </c>
       <c r="L73">
-        <v>9.9312871764815319E-2</v>
+        <v>0.33309194745150211</v>
+      </c>
+      <c r="N73" t="s">
+        <v>119</v>
+      </c>
+      <c r="O73" t="s">
+        <v>107</v>
+      </c>
+      <c r="P73" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>121</v>
+      </c>
+      <c r="R73" t="s">
+        <v>122</v>
+      </c>
+      <c r="S73" t="s">
+        <v>172</v>
+      </c>
+      <c r="T73" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="74" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C74" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D74" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E74">
         <v>2019</v>
       </c>
       <c r="F74">
-        <v>0.26</v>
+        <v>0.05</v>
       </c>
       <c r="G74">
         <v>1</v>
       </c>
       <c r="H74">
-        <v>1563.9999999999998</v>
+        <v>1836</v>
       </c>
       <c r="I74">
-        <v>39.6</v>
+        <v>46.8</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -7347,41 +7395,223 @@
         <v>36</v>
       </c>
       <c r="L74">
-        <v>0.49854352826201065</v>
+        <v>0.4985435282620107</v>
+      </c>
+      <c r="N74" t="s">
+        <v>119</v>
+      </c>
+      <c r="O74" t="s">
+        <v>109</v>
+      </c>
+      <c r="P74" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>121</v>
+      </c>
+      <c r="R74" t="s">
+        <v>122</v>
+      </c>
+      <c r="S74" t="s">
+        <v>172</v>
+      </c>
+      <c r="T74" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="75" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B75" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C75" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D75" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E75">
-        <v>2028</v>
+        <v>2013</v>
       </c>
       <c r="F75">
-        <v>0.3</v>
+        <v>1.4E-2</v>
       </c>
       <c r="G75">
         <v>1</v>
       </c>
       <c r="H75">
-        <v>1563.9999999999998</v>
+        <v>1836</v>
       </c>
       <c r="I75">
-        <v>39.6</v>
+        <v>46.800000000000004</v>
       </c>
       <c r="J75">
         <v>0</v>
       </c>
       <c r="K75">
+        <v>42</v>
+      </c>
+      <c r="L75">
+        <v>9.9312871764815305E-2</v>
+      </c>
+      <c r="N75" t="s">
+        <v>119</v>
+      </c>
+      <c r="O75" t="s">
+        <v>110</v>
+      </c>
+      <c r="P75" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>121</v>
+      </c>
+      <c r="R75" t="s">
+        <v>122</v>
+      </c>
+      <c r="S75" t="s">
+        <v>172</v>
+      </c>
+      <c r="T75" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B76" t="s">
+        <v>107</v>
+      </c>
+      <c r="C76" t="s">
+        <v>103</v>
+      </c>
+      <c r="D76" t="s">
+        <v>108</v>
+      </c>
+      <c r="E76">
+        <v>2015</v>
+      </c>
+      <c r="F76">
+        <v>1.15E-2</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76">
+        <v>1836</v>
+      </c>
+      <c r="I76">
+        <v>46.800000000000004</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>40</v>
+      </c>
+      <c r="L76">
+        <v>9.9312871764815305E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B77" t="s">
+        <v>107</v>
+      </c>
+      <c r="C77" t="s">
+        <v>103</v>
+      </c>
+      <c r="D77" t="s">
+        <v>108</v>
+      </c>
+      <c r="E77">
+        <v>2021</v>
+      </c>
+      <c r="F77">
+        <v>0.161</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77">
+        <v>1667.0559006211181</v>
+      </c>
+      <c r="I77">
+        <v>42.327950310559004</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>34</v>
+      </c>
+      <c r="L77">
+        <v>9.9312871764815319E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B78" t="s">
+        <v>109</v>
+      </c>
+      <c r="C78" t="s">
+        <v>103</v>
+      </c>
+      <c r="D78" t="s">
+        <v>106</v>
+      </c>
+      <c r="E78">
+        <v>2019</v>
+      </c>
+      <c r="F78">
+        <v>0.26</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78">
+        <v>1563.9999999999998</v>
+      </c>
+      <c r="I78">
+        <v>39.6</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>36</v>
+      </c>
+      <c r="L78">
+        <v>0.49854352826201065</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B79" t="s">
+        <v>110</v>
+      </c>
+      <c r="C79" t="s">
+        <v>103</v>
+      </c>
+      <c r="D79" t="s">
+        <v>111</v>
+      </c>
+      <c r="E79">
+        <v>2028</v>
+      </c>
+      <c r="F79">
+        <v>0.3</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
+      <c r="H79">
+        <v>1563.9999999999998</v>
+      </c>
+      <c r="I79">
+        <v>39.6</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
         <v>30</v>
       </c>
-      <c r="L75">
+      <c r="L79">
         <v>0.3404851337933279</v>
       </c>
     </row>
@@ -7391,7 +7621,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F1CD873-F493-4BBD-8695-DF11CE94FFD6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1307BEF-B108-4D51-B0C6-4AAA938A4495}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_KEN_grids_kan/vt_vervestacks_KEN_v1.xlsx
+++ b/VerveStacks_KEN_grids_kan/vt_vervestacks_KEN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD6CAEDB-0547-4229-9A22-BBF54F916A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1A2C407-EBAF-4BD4-A443-B9CB830DAC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{611109B2-678C-4D1F-9F4C-DFE0951E2F2F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{BCCFE558-D537-4A38-9CC4-7B837107D105}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1234,7 +1234,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{906DF3B9-7710-4C4B-9B77-E0D5D43559F0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5114DFAB-846D-4100-BA61-A2AAEF849526}">
   <dimension ref="B9:T18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1756,7 +1756,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48DF2DBC-6977-4729-A048-93870C15B10F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E7676A3-3211-477F-A48D-07DD168FBC0F}">
   <dimension ref="B9:T50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3971,7 +3971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8474A348-D0EB-441C-AF0D-FD861A7B5D08}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8CC5BDB-8539-4FE4-BA47-7DC7C15CFB6F}">
   <dimension ref="B9:T79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6956,7 +6956,7 @@
         <v>94</v>
       </c>
       <c r="P66" t="s">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="Q66" t="s">
         <v>121</v>
@@ -7012,7 +7012,7 @@
         <v>94</v>
       </c>
       <c r="P67" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="Q67" t="s">
         <v>121</v>
@@ -7621,7 +7621,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1307BEF-B108-4D51-B0C6-4AAA938A4495}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{907E1B0B-3C55-44D3-889D-F0E494801397}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_KEN_grids_kan/vt_vervestacks_KEN_v1.xlsx
+++ b/VerveStacks_KEN_grids_kan/vt_vervestacks_KEN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1A2C407-EBAF-4BD4-A443-B9CB830DAC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3885B998-1FF8-4D39-AB62-5101F220FA2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{BCCFE558-D537-4A38-9CC4-7B837107D105}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FB1906D3-6995-4B1F-82E0-B0E95ABBBA0F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1234,7 +1234,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5114DFAB-846D-4100-BA61-A2AAEF849526}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D156B6C-F371-409A-9669-7FAD5EE4126F}">
   <dimension ref="B9:T18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1756,7 +1756,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E7676A3-3211-477F-A48D-07DD168FBC0F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F361EA2-7EC9-459E-8169-860EF65CB095}">
   <dimension ref="B9:T50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3971,7 +3971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8CC5BDB-8539-4FE4-BA47-7DC7C15CFB6F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F2E160-E104-46DB-BCA8-81787B9A0E51}">
   <dimension ref="B9:T79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6956,7 +6956,7 @@
         <v>94</v>
       </c>
       <c r="P66" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="Q66" t="s">
         <v>121</v>
@@ -7012,7 +7012,7 @@
         <v>94</v>
       </c>
       <c r="P67" t="s">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="Q67" t="s">
         <v>121</v>
@@ -7621,7 +7621,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{907E1B0B-3C55-44D3-889D-F0E494801397}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A19DFBEB-38CB-4AAA-9E60-6EA76C8C9530}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_KEN_grids_kan/vt_vervestacks_KEN_v1.xlsx
+++ b/VerveStacks_KEN_grids_kan/vt_vervestacks_KEN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3885B998-1FF8-4D39-AB62-5101F220FA2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{89A651D5-0C05-42A9-B0D9-A1D0B4794F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FB1906D3-6995-4B1F-82E0-B0E95ABBBA0F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{10E0C656-6BFA-4ED1-98B5-F21AFE46882B}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1234,7 +1234,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D156B6C-F371-409A-9669-7FAD5EE4126F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF2DD301-02C4-42AB-9FC6-CAA55F4C8E13}">
   <dimension ref="B9:T18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1756,7 +1756,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F361EA2-7EC9-459E-8169-860EF65CB095}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F15413-5DFD-4ABA-9187-6FB6412926DA}">
   <dimension ref="B9:T50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3971,7 +3971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F2E160-E104-46DB-BCA8-81787B9A0E51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0AD7E39-5E9C-452C-9C77-CBE85F4724AF}">
   <dimension ref="B9:T79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6956,7 +6956,7 @@
         <v>94</v>
       </c>
       <c r="P66" t="s">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="Q66" t="s">
         <v>121</v>
@@ -7012,7 +7012,7 @@
         <v>94</v>
       </c>
       <c r="P67" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="Q67" t="s">
         <v>121</v>
@@ -7621,7 +7621,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A19DFBEB-38CB-4AAA-9E60-6EA76C8C9530}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{739313DF-62AF-4BEF-B216-7F0DC53B5499}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_KEN_grids_kan/vt_vervestacks_KEN_v1.xlsx
+++ b/VerveStacks_KEN_grids_kan/vt_vervestacks_KEN_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89A651D5-0C05-42A9-B0D9-A1D0B4794F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7154AF7-15AE-4069-B260-CDE73674D4A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{10E0C656-6BFA-4ED1-98B5-F21AFE46882B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F5E601E4-C2BB-4CFB-99B9-D665C3E17803}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1234,7 +1234,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF2DD301-02C4-42AB-9FC6-CAA55F4C8E13}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70A95CC9-765F-47BE-9FBC-4F5E6EDB91CD}">
   <dimension ref="B9:T18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1756,7 +1756,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F15413-5DFD-4ABA-9187-6FB6412926DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1061A910-8F0B-4157-B640-EB298A167C48}">
   <dimension ref="B9:T50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3971,7 +3971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0AD7E39-5E9C-452C-9C77-CBE85F4724AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23E12E7D-D81F-4975-9329-25B6C692AF38}">
   <dimension ref="B9:T79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6956,7 +6956,7 @@
         <v>94</v>
       </c>
       <c r="P66" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="Q66" t="s">
         <v>121</v>
@@ -7012,7 +7012,7 @@
         <v>94</v>
       </c>
       <c r="P67" t="s">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="Q67" t="s">
         <v>121</v>
@@ -7621,7 +7621,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{739313DF-62AF-4BEF-B216-7F0DC53B5499}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95A9E19E-4C01-4382-9DE8-F414DBF4C5F1}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_KEN_grids_kan/vt_vervestacks_KEN_v1.xlsx
+++ b/VerveStacks_KEN_grids_kan/vt_vervestacks_KEN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7154AF7-15AE-4069-B260-CDE73674D4A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4721EAE6-5D96-47AC-88D2-E45A661C07EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F5E601E4-C2BB-4CFB-99B9-D665C3E17803}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{501475FC-7377-4880-BEA1-08492FB35CF5}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1234,7 +1234,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70A95CC9-765F-47BE-9FBC-4F5E6EDB91CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A070ECC-B2EC-4142-AC54-A0CCC0373816}">
   <dimension ref="B9:T18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1756,7 +1756,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1061A910-8F0B-4157-B640-EB298A167C48}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AEF330A-1523-4094-9974-ECB1BB6D7DA9}">
   <dimension ref="B9:T50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3971,7 +3971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23E12E7D-D81F-4975-9329-25B6C692AF38}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD1542B7-E2FE-47EB-97FC-3450354673EC}">
   <dimension ref="B9:T79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7621,7 +7621,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95A9E19E-4C01-4382-9DE8-F414DBF4C5F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B52D27D3-5E05-4255-9790-F17C6484D849}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_KEN_grids_kan/vt_vervestacks_KEN_v1.xlsx
+++ b/VerveStacks_KEN_grids_kan/vt_vervestacks_KEN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4721EAE6-5D96-47AC-88D2-E45A661C07EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B119818-2700-4B3C-91A0-842CEEC47D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{501475FC-7377-4880-BEA1-08492FB35CF5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{07129F38-3D8D-4534-BF79-A2D091C91102}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1234,7 +1234,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A070ECC-B2EC-4142-AC54-A0CCC0373816}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B00233C-B050-4123-BA66-DA9CA4432BD8}">
   <dimension ref="B9:T18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1756,7 +1756,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AEF330A-1523-4094-9974-ECB1BB6D7DA9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C54F5770-3651-497C-AFAA-4BBFD523046A}">
   <dimension ref="B9:T50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3971,7 +3971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD1542B7-E2FE-47EB-97FC-3450354673EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CAE44EF-8C8E-41E0-8B25-91B8BE74E390}">
   <dimension ref="B9:T79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6956,7 +6956,7 @@
         <v>94</v>
       </c>
       <c r="P66" t="s">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="Q66" t="s">
         <v>121</v>
@@ -7012,7 +7012,7 @@
         <v>94</v>
       </c>
       <c r="P67" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="Q67" t="s">
         <v>121</v>
@@ -7621,7 +7621,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B52D27D3-5E05-4255-9790-F17C6484D849}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E9A0F93-5279-44B0-AC95-C301F4920340}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_KEN_grids_kan/vt_vervestacks_KEN_v1.xlsx
+++ b/VerveStacks_KEN_grids_kan/vt_vervestacks_KEN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B119818-2700-4B3C-91A0-842CEEC47D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E514E531-8DC4-497C-86C3-3116CCF1D43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{07129F38-3D8D-4534-BF79-A2D091C91102}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D8B4F205-B1DF-45FC-A885-8557232525C0}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1234,7 +1234,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B00233C-B050-4123-BA66-DA9CA4432BD8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20A5946-8627-48C3-8E36-2B60A78610B5}">
   <dimension ref="B9:T18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1756,7 +1756,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C54F5770-3651-497C-AFAA-4BBFD523046A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF56782-9639-45DE-B762-8EF5878C541C}">
   <dimension ref="B9:T50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3971,7 +3971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CAE44EF-8C8E-41E0-8B25-91B8BE74E390}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13761092-E0E3-4CFA-A60E-5A0E759C323D}">
   <dimension ref="B9:T79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7621,7 +7621,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E9A0F93-5279-44B0-AC95-C301F4920340}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{198CD578-DC85-4638-A5BE-498C5E26622F}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_KEN_grids_kan/vt_vervestacks_KEN_v1.xlsx
+++ b/VerveStacks_KEN_grids_kan/vt_vervestacks_KEN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E514E531-8DC4-497C-86C3-3116CCF1D43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{81B05623-5F8A-4D82-AE52-6315C966E501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D8B4F205-B1DF-45FC-A885-8557232525C0}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1E075123-07F6-492B-AA97-756A16136078}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1234,7 +1234,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20A5946-8627-48C3-8E36-2B60A78610B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E830825C-3303-4DD9-B629-C0DE8B63A0CB}">
   <dimension ref="B9:T18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1756,7 +1756,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF56782-9639-45DE-B762-8EF5878C541C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C9E9339-4CB6-416E-9F7A-076DA9984042}">
   <dimension ref="B9:T50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3971,7 +3971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13761092-E0E3-4CFA-A60E-5A0E759C323D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BB4F1CE-B7F5-47FE-8358-EBDDAC4B2CF7}">
   <dimension ref="B9:T79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6956,7 +6956,7 @@
         <v>94</v>
       </c>
       <c r="P66" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="Q66" t="s">
         <v>121</v>
@@ -7012,7 +7012,7 @@
         <v>94</v>
       </c>
       <c r="P67" t="s">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="Q67" t="s">
         <v>121</v>
@@ -7621,7 +7621,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{198CD578-DC85-4638-A5BE-498C5E26622F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27075EEF-026D-4999-A0B5-AFA89A4D634F}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
